--- a/data/trans_orig/IP07C13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C13-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>31465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76020</t>
+          <t>76230</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>28285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>22720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34338</t>
+          <t>33819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25668</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38967</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>27939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>16820</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20910</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>32187</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>27919</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>59329</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>75248</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,82 +4952,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
+          <t>36,94%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>16713</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>11672</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>22771</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>42,69%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>29892</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>22655</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>28,81%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t>37,16%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>16713</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>11663</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>42,67%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>29892</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>22956</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>38210</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>28,81%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>42636</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>59553</t>
+          <t>58655</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>77338</t>
+          <t>78268</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>41951</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25302</t>
+          <t>24951</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>38146</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>76284</t>
+          <t>76684</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>133529</t>
+          <t>134832</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>162688</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>189519</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>342651</t>
+          <t>342868</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>103672</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>131644</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>99791</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>126102</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>213939</t>
+          <t>212815</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>251174</t>
+          <t>250509</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,82 +6542,82 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>8847</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>4460</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>9023</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>46050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>40895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>40047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>75002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87756</t>
+          <t>88164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>19537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30771</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>41874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20829</t>
+          <t>20108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37655</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23080</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>27536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42006</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36017</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35054</t>
+          <t>35017</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>15786</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28205</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>34649</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>41728</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>56294</t>
+          <t>56126</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>73260</t>
+          <t>72975</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25176</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>42448</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,39 +11665,39 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>31394</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>45858</t>
+          <t>46058</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>62591</t>
+          <t>62381</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>82312</t>
+          <t>82504</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44159</t>
+          <t>43927</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26942</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>41224</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>60789</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>80802</t>
+          <t>81193</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>166825</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>195940</t>
+          <t>194972</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>194093</t>
+          <t>192686</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>223353</t>
+          <t>220965</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>367535</t>
+          <t>369661</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>410143</t>
+          <t>410537</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>117377</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>83841</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>111232</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>179967</t>
+          <t>178860</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30562</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>41690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38521</t>
+          <t>38229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>48506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72496</t>
+          <t>72189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>88099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>19366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>28184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16135</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>51828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32479</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52003</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22046</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15044</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>34342</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>47378</t>
+          <t>47236</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>67820</t>
+          <t>67428</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>86376</t>
+          <t>86042</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32269</t>
+          <t>32773</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>49675</t>
+          <t>50317</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>30186</t>
+          <t>30530</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46876</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>65912</t>
+          <t>65996</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>52755</t>
+          <t>52578</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>30796</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>45334</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>72811</t>
+          <t>73053</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92894</t>
+          <t>93420</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>803</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>178355</t>
+          <t>178210</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>208211</t>
+          <t>208269</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>192947</t>
+          <t>193436</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>223949</t>
+          <t>225122</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>380049</t>
+          <t>380194</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>422422</t>
+          <t>424561</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>108685</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>99605</t>
+          <t>101107</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>130178</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>217171</t>
+          <t>217140</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>259697</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>54780</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
